--- a/LISTAS/mi/SOPORTE ZAMAC DISMAY.xlsx
+++ b/LISTAS/mi/SOPORTE ZAMAC DISMAY.xlsx
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col width="12.5703125" customWidth="1" style="21" min="1" max="1"/>
@@ -796,12 +796,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45189.54995629737</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
+        <v>45232</v>
+      </c>
+    </row>
     <row r="5" ht="22.5" customHeight="1" s="21">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -840,18 +837,6 @@
       </c>
       <c r="E9" s="6" t="n"/>
     </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22" ht="18" customHeight="1" s="21">
       <c r="A22" s="11" t="inlineStr">
         <is>
@@ -915,7 +900,7 @@
       </c>
       <c r="C25" s="18" t="n"/>
       <c r="D25" s="13" t="n">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" ht="19.5" customHeight="1" s="21">
@@ -941,11 +926,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33" ht="19.5" customHeight="1" s="21"/>
     <row r="34" ht="14.25" customHeight="1" s="21"/>
     <row r="35" ht="18" customHeight="1" s="21">
@@ -978,22 +958,23 @@
         </is>
       </c>
       <c r="C36" s="15" t="n"/>
-      <c r="D36" s="10" t="n"/>
-    </row>
-    <row r="37"/>
+      <c r="D36" s="10" t="n">
+        <v>192.98</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B24:C24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE ZAMAC DISMAY.xlsx
+++ b/LISTAS/mi/SOPORTE ZAMAC DISMAY.xlsx
@@ -796,7 +796,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45232</v>
+        <v>45253</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1" s="21">

--- a/LISTAS/mi/SOPORTE ZAMAC DISMAY.xlsx
+++ b/LISTAS/mi/SOPORTE ZAMAC DISMAY.xlsx
@@ -796,7 +796,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1" s="21">

--- a/LISTAS/mi/SOPORTE ZAMAC DISMAY.xlsx
+++ b/LISTAS/mi/SOPORTE ZAMAC DISMAY.xlsx
@@ -796,7 +796,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1" s="21">

--- a/LISTAS/mi/SOPORTE ZAMAC DISMAY.xlsx
+++ b/LISTAS/mi/SOPORTE ZAMAC DISMAY.xlsx
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col width="12.5703125" customWidth="1" style="21" min="1" max="1"/>
@@ -796,9 +796,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45266</v>
-      </c>
-    </row>
+        <v>45225.50784709961</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5" ht="22.5" customHeight="1" s="21">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -837,6 +840,18 @@
       </c>
       <c r="E9" s="6" t="n"/>
     </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22" ht="18" customHeight="1" s="21">
       <c r="A22" s="11" t="inlineStr">
         <is>
@@ -868,7 +883,7 @@
       </c>
       <c r="C23" s="18" t="n"/>
       <c r="D23" s="13" t="n">
-        <v>398</v>
+        <v>533</v>
       </c>
     </row>
     <row r="24" ht="19.5" customHeight="1" s="21">
@@ -884,7 +899,7 @@
       </c>
       <c r="C24" s="18" t="n"/>
       <c r="D24" s="13" t="n">
-        <v>398</v>
+        <v>533</v>
       </c>
     </row>
     <row r="25" ht="19.5" customHeight="1" s="21">
@@ -900,7 +915,7 @@
       </c>
       <c r="C25" s="18" t="n"/>
       <c r="D25" s="13" t="n">
-        <v>400</v>
+        <v>533</v>
       </c>
     </row>
     <row r="26" ht="19.5" customHeight="1" s="21">
@@ -916,7 +931,7 @@
       </c>
       <c r="C26" s="15" t="n"/>
       <c r="D26" s="13" t="n">
-        <v>398</v>
+        <v>533</v>
       </c>
     </row>
     <row r="27">
@@ -926,6 +941,11 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33" ht="19.5" customHeight="1" s="21"/>
     <row r="34" ht="14.25" customHeight="1" s="21"/>
     <row r="35" ht="18" customHeight="1" s="21">
@@ -958,23 +978,22 @@
         </is>
       </c>
       <c r="C36" s="15" t="n"/>
-      <c r="D36" s="10" t="n">
-        <v>192.98</v>
-      </c>
-    </row>
+      <c r="D36" s="10" t="n"/>
+    </row>
+    <row r="37"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B23:C23"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B24:C24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE ZAMAC DISMAY.xlsx
+++ b/LISTAS/mi/SOPORTE ZAMAC DISMAY.xlsx
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col width="12.5703125" customWidth="1" style="21" min="1" max="1"/>
@@ -796,12 +796,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45225.50784709961</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
+        <v>45286</v>
+      </c>
+    </row>
     <row r="5" ht="22.5" customHeight="1" s="21">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -840,18 +837,6 @@
       </c>
       <c r="E9" s="6" t="n"/>
     </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22" ht="18" customHeight="1" s="21">
       <c r="A22" s="11" t="inlineStr">
         <is>
@@ -883,7 +868,7 @@
       </c>
       <c r="C23" s="18" t="n"/>
       <c r="D23" s="13" t="n">
-        <v>533</v>
+        <v>398</v>
       </c>
     </row>
     <row r="24" ht="19.5" customHeight="1" s="21">
@@ -899,7 +884,7 @@
       </c>
       <c r="C24" s="18" t="n"/>
       <c r="D24" s="13" t="n">
-        <v>533</v>
+        <v>398</v>
       </c>
     </row>
     <row r="25" ht="19.5" customHeight="1" s="21">
@@ -915,7 +900,7 @@
       </c>
       <c r="C25" s="18" t="n"/>
       <c r="D25" s="13" t="n">
-        <v>533</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" ht="19.5" customHeight="1" s="21">
@@ -931,7 +916,7 @@
       </c>
       <c r="C26" s="15" t="n"/>
       <c r="D26" s="13" t="n">
-        <v>533</v>
+        <v>398</v>
       </c>
     </row>
     <row r="27">
@@ -941,11 +926,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33" ht="19.5" customHeight="1" s="21"/>
     <row r="34" ht="14.25" customHeight="1" s="21"/>
     <row r="35" ht="18" customHeight="1" s="21">
@@ -980,20 +960,19 @@
       <c r="C36" s="15" t="n"/>
       <c r="D36" s="10" t="n"/>
     </row>
-    <row r="37"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A7:D7"/>
-    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B24:C24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
